--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487469_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487469_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5561</v>
+        <v>3.6095</v>
       </c>
       <c r="E2" t="n">
         <v>2.3941</v>
       </c>
       <c r="F2" t="n">
-        <v>1.162</v>
+        <v>1.2154</v>
       </c>
       <c r="G2" t="n">
         <v>0.8143</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2583</v>
+        <v>-1.2048</v>
       </c>
       <c r="T2" t="n">
         <v>-0.7722</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.486</v>
+        <v>-0.4326</v>
       </c>
       <c r="V2" t="n">
         <v>2.4332</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5047</v>
+        <v>1.4782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9356</v>
+        <v>0.9091</v>
       </c>
       <c r="F3" t="n">
         <v>0.5691000000000001</v>
@@ -688,10 +688,10 @@
         <v>0.9792</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6887</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3276</v>
+        <v>-0.3541</v>
       </c>
       <c r="U3" t="n">
         <v>-0.3611</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SERQUEIRA ALVAREZ</t>
+          <t>P. FERNÁNDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3093</v>
+        <v>-0.1285</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0594</v>
+        <v>-1.785</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2499</v>
+        <v>1.6566</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2677</v>
+        <v>0.5885</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1364</v>
+        <v>-0.1631</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4042</v>
+        <v>0.7516</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.6292</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.3077</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.3215</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2677</v>
+        <v>-0.0407</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1364</v>
+        <v>-0.4708</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4042</v>
+        <v>0.4301</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.3294</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0416</v>
+        <v>-1.4243</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0594</v>
+        <v>-1.518</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0178</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.8825</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNÁNDEZ CARBALLO</t>
+          <t>P. SERQUEIRA ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3777</v>
+        <v>-0.2826</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1679</v>
+        <v>-0.0594</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7902</v>
+        <v>-0.2232</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5885</v>
+        <v>-0.2677</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1631</v>
+        <v>0.1364</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7516</v>
+        <v>-0.4042</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6292</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3077</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3215</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0407</v>
+        <v>-0.2677</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4708</v>
+        <v>0.1364</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4301</v>
+        <v>-0.4042</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3294</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1543</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6735</v>
+        <v>-0.0149</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.9009</v>
+        <v>-0.0594</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2273</v>
+        <v>0.0446</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8825</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3715</v>
+        <v>-1.2168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7901</v>
+        <v>0.7042</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1617</v>
+        <v>-1.9211</v>
       </c>
       <c r="G6" t="n">
         <v>0.06519999999999999</v>
@@ -922,13 +922,13 @@
         <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.416</v>
+        <v>-0.2613</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.09</v>
+        <v>-0.1759</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.326</v>
+        <v>-0.0854</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2166</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4642</v>
+        <v>-1.442</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6382</v>
+        <v>-1.5359</v>
       </c>
       <c r="F7" t="n">
-        <v>0.174</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1975</v>
@@ -1000,13 +1000,13 @@
         <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.421</v>
+        <v>-0.3989</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0052</v>
+        <v>-0.0854</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8249</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8929</v>
+        <v>-1.6215</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1854</v>
+        <v>-0.7002</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7075</v>
+        <v>-0.9213</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9124</v>
@@ -1078,13 +1078,13 @@
         <v>2.3502</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5312</v>
+        <v>-1.2598</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.8415</v>
+        <v>-1.3562</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3103</v>
+        <v>0.0965</v>
       </c>
       <c r="V8" t="n">
         <v>0.5507</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9909</v>
+        <v>-2.178</v>
       </c>
       <c r="E9" t="n">
         <v>-1.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2909</v>
+        <v>-0.478</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3389</v>
@@ -1156,13 +1156,13 @@
         <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5517</v>
+        <v>-0.7388</v>
       </c>
       <c r="T9" t="n">
         <v>-1.1286</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5769</v>
+        <v>0.3898</v>
       </c>
       <c r="V9" t="n">
         <v>-1.492</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2917</v>
+        <v>-4.2113</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.868</v>
+        <v>-1.8945</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4237</v>
+        <v>-2.3168</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0982</v>
@@ -1234,13 +1234,13 @@
         <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.152</v>
+        <v>-1.0716</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2186</v>
+        <v>-1.2451</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1735</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8249</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8531</v>
+        <v>-4.6066</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8844</v>
+        <v>-4.825</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0312</v>
+        <v>0.2183</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6379</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.585</v>
+        <v>-1.3385</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.188</v>
+        <v>-1.1286</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3969</v>
+        <v>-0.2098</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8260999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.4905</v>
+        <v>-10.5996</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.383500000000002</v>
+        <v>-8.492599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.107200000000001</v>
+        <v>-2.1072</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7912</v>
@@ -1390,13 +1390,13 @@
         <v>13.7092</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.319000000000001</v>
+        <v>-8.428100000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.942600000000001</v>
+        <v>-8.051599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3762999999999999</v>
+        <v>-0.3762</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3181</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.7394</v>
+        <v>6.6351</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4368</v>
+        <v>5.0275</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3026</v>
+        <v>1.6076</v>
       </c>
       <c r="G13" t="n">
         <v>3.9164</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8438</v>
+        <v>1.7394</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8651</v>
+        <v>0.4558</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9786</v>
+        <v>1.2836</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3566</v>
+        <v>4.0867</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0382</v>
+        <v>4.4475</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6816</v>
+        <v>-0.3608</v>
       </c>
       <c r="G14" t="n">
         <v>4.2024</v>
@@ -1546,13 +1546,13 @@
         <v>0.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0832</v>
+        <v>0.6469</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.891</v>
+        <v>-0.4817</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8079</v>
+        <v>1.1286</v>
       </c>
       <c r="V14" t="n">
         <v>0.6083</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6481</v>
+        <v>1.9409</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3772</v>
+        <v>-1.2982</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0253</v>
+        <v>3.2392</v>
       </c>
       <c r="G15" t="n">
         <v>1.0021</v>
@@ -1624,13 +1624,13 @@
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3498</v>
+        <v>1.6427</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5474</v>
+        <v>0.6264</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8025</v>
+        <v>1.0163</v>
       </c>
       <c r="V15" t="n">
         <v>0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4331</v>
+        <v>1.2097</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5227</v>
+        <v>0.1923</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9104</v>
+        <v>1.0174</v>
       </c>
       <c r="G16" t="n">
         <v>0.0605</v>
@@ -1702,13 +1702,13 @@
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7055</v>
+        <v>1.4821</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8379</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8676</v>
+        <v>0.9745</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3329</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.9102</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1213</v>
+        <v>-2.0145</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5506</v>
+        <v>2.9248</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6514</v>
+        <v>-1.1586</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7027</v>
+        <v>-0.7037</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3541</v>
+        <v>-0.4549</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-1.3867</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0204</v>
+        <v>-1.3203</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6822</v>
+        <v>-0.0664</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0104</v>
+        <v>0.228</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6822</v>
+        <v>0.6166</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.3886</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.3917</v>
+        <v>-1.3709</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1067</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0418</v>
+        <v>0.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1485</v>
+        <v>0.6599</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2166</v>
+        <v>1.159</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>0.4931</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3985</v>
+        <v>0.9079</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5262</v>
+        <v>0.2237</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9248</v>
+        <v>0.6842</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1586</v>
+        <v>-0.6514</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7037</v>
+        <v>0.7027</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4549</v>
+        <v>-1.3541</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3867</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3203</v>
+        <v>0.0204</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0664</v>
+        <v>-0.6822</v>
       </c>
       <c r="M18" t="n">
-        <v>0.228</v>
+        <v>0.0104</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6166</v>
+        <v>0.6822</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3886</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3709</v>
+        <v>-0.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3982</v>
+        <v>0.3427</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2617</v>
+        <v>0.0606</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6599</v>
+        <v>0.2822</v>
       </c>
       <c r="V18" t="n">
-        <v>1.159</v>
+        <v>1.2166</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4931</v>
+        <v>1.2166</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>M. SYLLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1481</v>
+        <v>0.2248</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6464</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7944</v>
+        <v>0.2967</v>
       </c>
       <c r="G19" t="n">
-        <v>1.085</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0242</v>
+        <v>0.0892</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9392</v>
+        <v>0.0052</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5299</v>
+        <v>0.0204</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4086</v>
+        <v>0.0204</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1212</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4449</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6156</v>
+        <v>0.0687</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0604</v>
+        <v>0.0052</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3294</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0215</v>
+        <v>0.1304</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3388</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3603</v>
+        <v>0.2228</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SYLLA</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1136</v>
+        <v>0.1656</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2766</v>
+        <v>-0.4417</v>
       </c>
       <c r="F20" t="n">
-        <v>0.163</v>
+        <v>0.6073</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09429999999999999</v>
+        <v>1.085</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0892</v>
+        <v>2.0242</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0052</v>
+        <v>-0.9392</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0204</v>
+        <v>1.5299</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0204</v>
+        <v>1.4086</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.1212</v>
       </c>
       <c r="M20" t="n">
-        <v>0.07389999999999999</v>
+        <v>-0.4449</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0687</v>
+        <v>0.6156</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0052</v>
+        <v>-1.0604</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.3294</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2079</v>
+        <v>1.0391</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.297</v>
+        <v>-0.1341</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0891</v>
+        <v>1.1732</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. FRAGA CANTELAR</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2598</v>
+        <v>0.0542</v>
       </c>
       <c r="E21" t="n">
-        <v>0.647</v>
+        <v>-0.9858</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9069</v>
+        <v>1.0401</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7016</v>
+        <v>-1.6865</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1558</v>
+        <v>-0.9283</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5458</v>
+        <v>-0.7582</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3181</v>
+        <v>-1.1042</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0003</v>
+        <v>-0.32</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6822</v>
+        <v>-0.7842</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0197</v>
+        <v>-0.5823</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1562</v>
+        <v>-0.6083</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1364</v>
+        <v>0.026</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3624</v>
+        <v>0.9781</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2794</v>
+        <v>-0.157</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.083</v>
+        <v>1.1351</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6083</v>
+        <v>-0.6083</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>B. FRAGA CANTELAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4483</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7022</v>
+        <v>0.7494</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2539</v>
+        <v>-0.8267</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6865</v>
+        <v>-0.7016</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9283</v>
+        <v>-0.1558</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7582</v>
+        <v>-0.5458</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1042</v>
+        <v>0.3181</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.32</v>
+        <v>1.0003</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7842</v>
+        <v>-0.6822</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5823</v>
+        <v>-1.0197</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6083</v>
+        <v>-1.1562</v>
       </c>
       <c r="O22" t="n">
-        <v>0.026</v>
+        <v>0.1364</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4756</v>
+        <v>-0.1798</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8734</v>
+        <v>-0.177</v>
       </c>
       <c r="U22" t="n">
-        <v>1.349</v>
+        <v>-0.0028</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6083</v>
+        <v>0.6083</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8183</v>
+        <v>-0.7473</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0859</v>
+        <v>0.2905</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9042</v>
+        <v>-1.0378</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2044</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3861</v>
+        <v>0.4571</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.6683</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2653</v>
+        <v>-3.82</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2163</v>
+        <v>-4.0117</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0489</v>
+        <v>0.1916</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1671</v>
@@ -2326,13 +2326,13 @@
         <v>0.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3148</v>
+        <v>0.1304</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4752</v>
+        <v>-0.2705</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1604</v>
+        <v>0.401</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11.4904</v>
+        <v>11.4905</v>
       </c>
       <c r="E25" t="n">
-        <v>2.107</v>
+        <v>2.107099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>9.3834</v>
+        <v>9.383599999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7911</v>
+        <v>2.791099999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>7.489100000000001</v>
+        <v>7.4891</v>
       </c>
       <c r="I25" t="n">
         <v>-4.697800000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-5.906599999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.937799999999999</v>
+        <v>-2.9378</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.7093</v>
@@ -2407,10 +2407,10 @@
         <v>9.318900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3763000000000004</v>
+        <v>0.3766999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>8.942699999999999</v>
+        <v>8.9427</v>
       </c>
       <c r="V25" t="n">
         <v>2.3181</v>
